--- a/sports_forms/027_winter_sports_parent_meeting_rsvp--sports_forms.xlsx
+++ b/sports_forms/027_winter_sports_parent_meeting_rsvp--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'option_1',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'option_1', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'option_2',_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'option_2', 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -739,29 +739,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'option_3',_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'option_3', 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other_(please_specify)'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'other', 'label': 'Other (please specify)'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -773,29 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'option_1',_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'option_1', 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>question_2_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'name':_'option_2',_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'name': 'option_2', 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
